--- a/utils/monday_sprint_sprint_2024-49.xlsx
+++ b/utils/monday_sprint_sprint_2024-49.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="160">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>28586</t>
+    <t>7823416990</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>11/11/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>23/11/2024</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -102,7 +102,7 @@
     <t>Novembro</t>
   </si>
   <si>
-    <t>28262</t>
+    <t>7823643556</t>
   </si>
   <si>
     <t>Revisão de PDI’s:</t>
@@ -111,13 +111,13 @@
     <t>Média</t>
   </si>
   <si>
+    <t>13/11/2024</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>28739</t>
+    <t>7814928565</t>
   </si>
   <si>
     <t>Saldo pré-lista almoxarifado</t>
@@ -126,67 +126,82 @@
     <t>08/11/2024</t>
   </si>
   <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>7823643576</t>
+  </si>
+  <si>
     <t>Preenchimento dos PDI’s</t>
   </si>
   <si>
-    <t>28379</t>
+    <t>7823417029</t>
   </si>
   <si>
     <t>Apontamento Horímetro Deltractor</t>
   </si>
   <si>
-    <t>28738</t>
+    <t>7814948704</t>
   </si>
   <si>
     <t>Relatório de retidos</t>
   </si>
   <si>
-    <t>28707</t>
+    <t>7814998181</t>
   </si>
   <si>
     <t>Ordenação - Regra do Planilha do MPS</t>
   </si>
   <si>
-    <t>28679</t>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>7815034473</t>
   </si>
   <si>
     <t>AJUSTAR TELA ESTORNO DE REQUISIÇÃO</t>
   </si>
   <si>
-    <t>28663</t>
+    <t>7815094926</t>
   </si>
   <si>
     <t>Campo auxiliar em cadastro</t>
   </si>
   <si>
-    <t>28744</t>
+    <t>17/11/2024</t>
+  </si>
+  <si>
+    <t>7814907533</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Integrator - CC 1001 Inativo permitiu lançamento</t>
   </si>
   <si>
-    <t>28775</t>
+    <t>12/11/2024</t>
+  </si>
+  <si>
+    <t>7815311779</t>
   </si>
   <si>
     <t>ERRO Integração Relatório Custeio MP SISTEMA DE CORRIDAS x CUSTEIO</t>
   </si>
   <si>
-    <t>28767</t>
+    <t>7824410706</t>
   </si>
   <si>
     <t>Solicitação de melhoria no sistema de orçamento</t>
   </si>
   <si>
-    <t>28634</t>
+    <t>7815349116</t>
   </si>
   <si>
     <t>REFERÊNCIA DE ROTEIRO PRELIMINAR</t>
   </si>
   <si>
-    <t>28837</t>
+    <t>7926108358</t>
   </si>
   <si>
     <t>Alteração view funcionários - Sênor</t>
@@ -195,16 +210,19 @@
     <t>25/11/2024</t>
   </si>
   <si>
+    <t>24/11/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>28771</t>
+    <t>7814890950</t>
   </si>
   <si>
     <t>Melhoria no calculo de tempos e inclusão de registro de motivos de não atendimento - Painel TV Komatsu</t>
   </si>
   <si>
-    <t>28669</t>
+    <t>7832272440</t>
   </si>
   <si>
     <t>Correção</t>
@@ -213,18 +231,15 @@
     <t>Informações de movimentação do gestão a vista</t>
   </si>
   <si>
-    <t>12/11/2024</t>
-  </si>
-  <si>
-    <t>28808</t>
+    <t>20/11/2024</t>
+  </si>
+  <si>
+    <t>7842411370</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Campo Espécie - Exportação Imobilizado</t>
   </si>
   <si>
-    <t>13/11/2024</t>
-  </si>
-  <si>
     <t>7823493797</t>
   </si>
   <si>
@@ -234,7 +249,7 @@
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento - Reunião</t>
   </si>
   <si>
-    <t>26329</t>
+    <t>6980106023</t>
   </si>
   <si>
     <t>Amarrar etiqueta de saida da Magayver com Cód Altona e Cód. De Barras ou QR CODE com as informações da solicitação.</t>
@@ -243,13 +258,16 @@
     <t>08/07/2024</t>
   </si>
   <si>
+    <t>10/11/2024</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
     <t>Julho</t>
   </si>
   <si>
-    <t>28348</t>
+    <t>7751947954</t>
   </si>
   <si>
     <t>Na consulta plano de ação, permitir visualizar todos, mas só alterar os planos de ação dos indicadores do usuário logado</t>
@@ -264,67 +282,91 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>7823417056</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
   </si>
   <si>
+    <t>7823643490</t>
+  </si>
+  <si>
     <t>Preenchimento das cotas</t>
   </si>
   <si>
+    <t>7823643528</t>
+  </si>
+  <si>
     <t>Consulta de PDI’s preenchidos</t>
   </si>
   <si>
-    <t>28589</t>
+    <t>7823643607</t>
   </si>
   <si>
     <t>PDI_CheckList - Campo Livre para observações.</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7823695949</t>
   </si>
   <si>
     <t>Controle de Eventos Financeiros - Verificar cobrança conforme alocação</t>
   </si>
   <si>
-    <t>26510</t>
+    <t>7823493714</t>
   </si>
   <si>
     <t>PROEX Financeiro (Sinalizar Status PROEX)</t>
   </si>
   <si>
+    <t>7751952365</t>
+  </si>
+  <si>
     <t>Ajustar o gráfico para usar toda a tela inicial. Colocar sinaleiro dentro do frame</t>
   </si>
   <si>
+    <t>7823643623</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew - Alterna cores nas colunas da sequências.</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>7815633218</t>
   </si>
   <si>
     <t>Ordem de Coleta e Entrega (Controle de Pátio)</t>
   </si>
   <si>
+    <t>7832406059</t>
+  </si>
+  <si>
     <t>Tela de login de fornecedor e transportadora</t>
   </si>
   <si>
+    <t>7832408667</t>
+  </si>
+  <si>
     <t>Compras - Identificação pela Ordem de Compra</t>
   </si>
   <si>
+    <t>7832410837</t>
+  </si>
+  <si>
     <t>Vendas – Motorista identifica pela Ordem de Coleta</t>
   </si>
   <si>
-    <t>28482</t>
+    <t>7823398047</t>
   </si>
   <si>
     <t>Relatório Faturamento por Sequência (Out/23 a Set/24</t>
   </si>
   <si>
+    <t>7832415058</t>
+  </si>
+  <si>
     <t>Criar "Ordem de coleta" que recebe o recibo de embarque</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>7823376236</t>
   </si>
   <si>
     <t>Ajuste no sistema BLOCO K</t>
@@ -348,19 +390,19 @@
     <t>Cadastros dos machos na FTF</t>
   </si>
   <si>
-    <t>28722</t>
+    <t>7814971785</t>
   </si>
   <si>
     <t>Melhorias Fastloop e ULE</t>
   </si>
   <si>
-    <t>28686</t>
+    <t>7815012830</t>
   </si>
   <si>
     <t>Síntese de reunião Chamado 28348 - Indicadores da GIQ</t>
   </si>
   <si>
-    <t>28593</t>
+    <t>7815711182</t>
   </si>
   <si>
     <t>Solda Divergências - QLIKSENSE</t>
@@ -372,7 +414,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-49</t>
+    <t>Jul/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1011,13 +1053,13 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1058,10 +1100,10 @@
         <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>26</v>
@@ -1075,7 +1117,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1087,10 +1129,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1105,13 +1147,13 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1122,7 +1164,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1134,10 +1176,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1169,7 +1211,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1181,10 +1223,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1199,10 +1241,10 @@
         <v>36</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>26</v>
@@ -1216,7 +1258,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1228,10 +1270,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1246,10 +1288,10 @@
         <v>36</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>26</v>
@@ -1263,7 +1305,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1275,10 +1317,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -1293,10 +1335,10 @@
         <v>36</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
@@ -1310,7 +1352,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1322,10 +1364,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1340,10 +1382,10 @@
         <v>36</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>26</v>
@@ -1357,7 +1399,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1369,10 +1411,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1387,10 +1429,10 @@
         <v>36</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -1404,7 +1446,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1416,10 +1458,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1434,10 +1476,10 @@
         <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
@@ -1451,7 +1493,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1463,10 +1505,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1484,7 +1526,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>26</v>
@@ -1498,7 +1540,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1510,10 +1552,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1531,7 +1573,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>26</v>
@@ -1545,7 +1587,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1557,10 +1599,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -1572,19 +1614,19 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1592,7 +1634,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1604,10 +1646,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -1625,7 +1667,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -1639,22 +1681,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -1666,13 +1708,13 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
@@ -1686,7 +1728,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1698,10 +1740,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1713,13 +1755,13 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1733,22 +1775,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -1763,10 +1805,10 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
@@ -1780,7 +1822,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1792,10 +1834,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -1807,27 +1849,27 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1839,10 +1881,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -1854,27 +1896,27 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1886,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1907,10 +1949,10 @@
         <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>27</v>
@@ -1921,7 +1963,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1933,10 +1975,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -1951,10 +1993,10 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -1968,7 +2010,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1980,10 +2022,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -1998,10 +2040,10 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2015,7 +2057,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2027,10 +2069,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2045,10 +2087,10 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
@@ -2062,22 +2104,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2095,10 +2137,10 @@
         <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
@@ -2109,7 +2151,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2121,10 +2163,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2156,7 +2198,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2168,10 +2210,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2183,27 +2225,27 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2215,10 +2257,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
@@ -2233,10 +2275,10 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2250,7 +2292,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2262,10 +2304,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2280,7 +2322,7 @@
         <v>36</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2297,7 +2339,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2309,10 +2351,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2324,13 +2366,13 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
@@ -2344,7 +2386,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2356,10 +2398,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2371,16 +2413,16 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -2391,7 +2433,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2403,10 +2445,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -2418,16 +2460,16 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -2438,7 +2480,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2450,10 +2492,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -2468,7 +2510,7 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2485,7 +2527,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2497,10 +2539,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
@@ -2512,13 +2554,13 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2532,7 +2574,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2544,10 +2586,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
@@ -2562,10 +2604,10 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>26</v>
@@ -2579,7 +2621,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2591,10 +2633,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -2606,19 +2648,19 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2626,7 +2668,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2638,10 +2680,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
@@ -2659,7 +2701,7 @@
         <v>24</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -2673,7 +2715,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2685,10 +2727,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
@@ -2703,13 +2745,13 @@
         <v>36</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
@@ -2720,7 +2762,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2732,10 +2774,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
@@ -2750,13 +2792,13 @@
         <v>36</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -2767,7 +2809,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2779,10 +2821,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -2797,13 +2839,13 @@
         <v>36</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>27</v>
@@ -2825,23 +2867,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2849,16 +2891,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2869,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2877,12 +2919,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22">
         <v>25</v>
@@ -2898,7 +2940,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2929,12 +2971,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -2948,7 +2990,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2958,25 +3000,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2993,19 +3035,19 @@
         <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10">
         <v>25</v>
@@ -3014,12 +3056,12 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -3034,24 +3076,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3063,47 +3105,41 @@
         <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
-      <c r="P13" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3117,7 +3153,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3125,7 +3161,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3133,7 +3169,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3141,10 +3177,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3152,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3160,142 +3196,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
